--- a/Operation-Mirror-Pivot-Finants.xlsx
+++ b/Operation-Mirror-Pivot-Finants.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kokkuvõte" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kliimaministeerium" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 rahaallikat" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vana vs Uus" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aasta 5 pilt" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inimeste Fond" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-sammuline pivot" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operation Mirror" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap raha" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERMA 5a" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Must turg vs legal" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Kokkuvõte" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Kliimaministeerium" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="4 rahaallikat" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Vana vs Uus" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Aasta 5 pilt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Inimeste Fond" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="5-sammuline pivot" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Operation Mirror" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Bootstrap raha" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="ERMA 5a" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Must turg vs legal" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Olessanded" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Finantsstrateegia" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +32,7 @@
     <numFmt numFmtId="164" formatCode="#,##0 &quot;€&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +50,11 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +91,16 @@
         <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001565C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006A1B9A"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -113,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -149,6 +164,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1006,7 +1031,7 @@
       <c r="E24" s="3" t="inlineStr"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>40% päike, 30% tööstus, 20% BI, 10% haridus</t>
+          <t>Dalio: 18 voogu; macro 40/30/20/10</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr"/>
@@ -1495,6 +1520,1540 @@
     </row>
   </sheetData>
   <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ÕLESSANDED ALLÜKSUSTELE — MALEVAPEALIKUD MAASTIKUL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Kiht</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Kes</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Mida teeb maastikul</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Mõju elanikele</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>A5 eesmärk</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Seos teiste kihtidega</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>7. OLESSANDED</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Malevapealik</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Koordineerib tsiviiltegevust</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Töökohad, turvalisus</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>15 maleva aktiivne</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Operation Mirror elluviija</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Õlg</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Malevkonna pealik</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Kuulab vallas/linnas</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Farmer↔KOV↔tarbija</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>150+ kuulamispunkti</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>ERMA nõudlus</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Õlg</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>JUP 2 lõpetaja</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Probleemide lahendaja</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Kriisikomisjonid</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>500+ juhti ühiskonnas</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>KOV Šveitsi mudel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Õlg</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Sõdurioskuste kursus</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Juhtimisoskused koju</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Iga KL liige = juht</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>10 000+ juhti</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Tasuta koolitus</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>KOV</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Otsused lähedal</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Kooli aiad, LEADER</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Kõik KOV kaasatud</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Puukoolid</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>ERMA / farmer</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Pakkumine</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Kohalik toode</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>30 puukooli</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Hemp Authority</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Tarbija</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Nõudlus</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Osta Eesti</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Reguleeritud turg</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Inimeste Fond</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>PILOOT 2026</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Sakala malev</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Viljandi, Tactical Foodpack</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Puukoolid</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>3 maleva</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Sverre võrgustik</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Jõgeva malev</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Sadala Agro, kanep</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Farmerid</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Nordic Hemp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Tartu malev</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>EPM, teadus</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Koolitus</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>ERMA klaster</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>MALEVAPEALIKU ÜLEANDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Ülesanne</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Sagedus</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Mõõdik</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Kulu</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Märkus</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Kohtumine KOV juhtidega</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Kvartaalselt</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Protokoll</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Järvamaa mudel</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Tsiviil-maastiku kaart</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>1×/a</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Farmerid, poed, koolid</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Anonüümne</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Nõudluse raport ERMA-le</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Kvartaalselt</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Osta Eesti statistika</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Maleva piirkond</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Kriisikoolitus (CIMIC)</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>1×/a</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Osalejad</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>LEADER/KL</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Partnerid kaasatud</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Noorte aiaprogramm</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Pidev</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Kotkad/Kodutütarde</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>KOV</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Loodus kooli</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>JUP suunamine tsiviilile</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Pidev</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Juhtide arv</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Sõdurioskuste export</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n"/>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>JUP → TSIVIIL PIPELINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Kursus</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Mida annab</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Kuhu liigub</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Näide</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Kool</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>A5 maht</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sõdurioskused / alus</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Meeskond, distsipliin</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Iga kodukohas</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>KL liige</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>KL kool</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>10 000+</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>JUP 1</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Juhtimise baas</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Meeskonnajuht</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Malevkond</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Alu mõis</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>2 000+</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>JUP 2</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Probleemi lahendus</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>KOV kriisikomisjon</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Järvamaa</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Alu mõis</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>500+</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>JUP 3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Ülesandekeskne juht</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Malevapealik</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>15 maleva</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Alu mõis</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>CIMIC koolitus</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Tsiviil-sõjaline</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Omavalitsus + partner</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Kriis</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Õõlg</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>15 KOV/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EESTI FINANTSSTRATEEGIA — 15–20 MITTE-KORRELATSIOONSET VOOGU (RAY DALIO / TONY ROBBINS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Põhimõte — Ray Dalio (Bridgewater): leia 15–20 mitte-korrelatsioonset tuluvoogu ja investeeri neisse. Tony Robbins populariseeris (*Money: Master the Game*, All Seasons portfell). Üks sektori krahh ei viib kogu portfelli alla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Tuluvoog / varaklass</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Korrelatsioon</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Siht %</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>A5 € (84M)</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Märkus</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Päikesepargid + salvestus</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Energia ≠ tarbimine</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E5" s="6">
+        <f>D4*84000000</f>
+        <v/>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>8× 5MW parki</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Liisingumasinad (tootlik vara)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>≠ börs</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E6" s="4">
+        <f>D5*84000000</f>
+        <v/>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Paid off → vaba kassa</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Tööstuskanep — kiud, eksport</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Ekspordi tsükkel</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E7" s="6">
+        <f>D6*84000000</f>
+        <v/>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Nordic Hemp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>CBD kosmeetika</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Tarbimine</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E8" s="4">
+        <f>D7*84000000</f>
+        <v/>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Kreemid, õlid</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Growshop võrgustik</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Kohalik müük</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E9" s="6">
+        <f>D8*84000000</f>
+        <v/>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Asendab importi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Reguleeritud täiskasvanute turg</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Siseriiklik</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E10" s="4">
+        <f>D9*84000000</f>
+        <v/>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Maksud + ohutus</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Meditsiiniline kanep</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Haigekassa</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E11" s="6">
+        <f>D10*84000000</f>
+        <v/>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Stabiilne ostja</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Puukoolid + seemikumüük</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Maaelu, ≠ börs</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E12" s="4">
+        <f>D11*84000000</f>
+        <v/>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>30 puukooli</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Kutsekool + koolitus</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Inimkapital</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E13" s="6">
+        <f>D12*84000000</f>
+        <v/>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Pipeline töökohtadele</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Operation Mirror säästud</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Bürokraatia efektiivsus</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E14" s="4">
+        <f>D13*84000000</f>
+        <v/>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>~€35M/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>LEADER / EAS / CAP</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Grantid, ≠ börs</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E15" s="6">
+        <f>D14*84000000</f>
+        <v/>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Olemasolev raha</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Urban farm + KOV aiad</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Kohalik kogukond</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E16" s="4">
+        <f>D15*84000000</f>
+        <v/>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Linn + maa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Teadus + patendid (EPM)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Pikaajaline</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E17" s="6">
+        <f>D16*84000000</f>
+        <v/>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Eksport tulevikus</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Hampcrete + ehitus</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Ehitustsükkel</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E18" s="4">
+        <f>D17*84000000</f>
+        <v/>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Avalik sektor</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Kriisitoit / varud</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Kriis, defensiivne</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E19" s="6">
+        <f>D18*84000000</f>
+        <v/>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>2-nädala reegel</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Turism + kogemuskeskus</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Hooajaline</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E20" s="4">
+        <f>D19*84000000</f>
+        <v/>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Farm visits</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>IT + IoT kasvatus</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Tehnoloogia</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E21" s="6">
+        <f>D20*84000000</f>
+        <v/>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Efektiivsus</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Basic income pilot</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Sotsiaal</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E22" s="3">
+        <f>D21*84000000</f>
+        <v/>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>10k × 200€/kuu</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>KOKKU (18 voogu)</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Dalio siht: 15–20</t>
+        </is>
+      </c>
+      <c r="D23" s="5">
+        <f>SUM(D4:D21)</f>
+        <v/>
+      </c>
+      <c r="E23" s="5">
+        <f>SUM(E4:E21)</f>
+        <v/>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>100% Inimeste Fond A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="9" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>4 kotti (vanem mudel)</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Endiselt kehtib</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Päikesepargid + salvestus</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E26" s="4">
+        <f>84000000*0.4</f>
+        <v/>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Macro ≠ voogude detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Tööstus + robotid</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E27" s="6">
+        <f>84000000*0.3</f>
+        <v/>
+      </c>
+      <c r="F27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Basic income pilot</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E28">
+        <f>84000000*0.2</f>
+        <v/>
+      </c>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Haridus + koolid + loodus</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E29">
+        <f>84000000*0.1</f>
+        <v/>
+      </c>
+      <c r="F29" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Operation-Mirror-Pivot-Finants.xlsx
+++ b/Operation-Mirror-Pivot-Finants.xlsx
@@ -1031,7 +1031,7 @@
       <c r="E24" s="3" t="inlineStr"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Dalio: 18 voogu; macro 40/30/20/10</t>
+          <t>Dalio: 8 voogu; macro 40/30/20/10</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr"/>
@@ -2346,7 +2346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2360,14 +2360,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>EESTI FINANTSSTRATEEGIA — 15–20 MITTE-KORRELATSIOONSET VOOGU (RAY DALIO / TONY ROBBINS)</t>
+          <t>EESTI FINANTSSTRATEEGIA — 8 MITTE-KORRELATSIOONSET VOOGU (RAY DALIO / TONY ROBBINS)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>Põhimõte — Ray Dalio (Bridgewater): leia 15–20 mitte-korrelatsioonset tuluvoogu ja investeeri neisse. Tony Robbins populariseeris (*Money: Master the Game*, All Seasons portfell). Üks sektori krahh ei viib kogu portfelli alla.</t>
+          <t>Põhimõte — Ray Dalio (Bridgewater): leia mitte-korrelatsioonseid tulovooge ja investeeri neisse (täisversioon 15–20). Eesti mudel: 8 voogu = macro 40/30/20/10. Tony Robbins: *Money: Master the Game*, All Seasons portfell.</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="E5" s="6">
         <f>D4*84000000</f>
@@ -2440,16 +2440,16 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Liisingumasinad (tootlik vara)</t>
+          <t>Liisingumasinad + robotid</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>≠ börs</t>
+          <t>Tootlik vara ≠ börs</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E6" s="4">
         <f>D5*84000000</f>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Tööstuskanep — kiud, eksport</t>
+          <t>Tööstuskanep + eksport + CBD</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E7" s="6">
         <f>D6*84000000</f>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Nordic Hemp</t>
+          <t>Kiud, kosmeetika</t>
         </is>
       </c>
     </row>
@@ -2498,16 +2498,16 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>CBD kosmeetika</t>
+          <t>Growshop + reguleeritud turg</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Tarbimine</t>
+          <t>Kohalik tarbimine</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E8" s="4">
         <f>D7*84000000</f>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Kreemid, õlid</t>
+          <t>Asendab importi</t>
         </is>
       </c>
     </row>
@@ -2527,16 +2527,16 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Growshop võrgustik</t>
+          <t>Puukoolid + maaelu (LEADER)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Kohalik müük</t>
+          <t>Maaelu ≠ börs</t>
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E9" s="6">
         <f>D8*84000000</f>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Asendab importi</t>
+          <t>30 puukooli</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Reguleeritud täiskasvanute turg</t>
+          <t>Haridus + kutsekool</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Siseriiklik</t>
+          <t>Inimkapital</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Maksud + ohutus</t>
+          <t>Uus eriala</t>
         </is>
       </c>
     </row>
@@ -2585,16 +2585,16 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Meditsiiniline kanep</t>
+          <t>Mirror säästud + teadus (EPM)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Haigekassa</t>
+          <t>Bürokraatia + pikaajaline</t>
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E11" s="6">
         <f>D10*84000000</f>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Stabiilne ostja</t>
+          <t>~€35M/a + patendid</t>
         </is>
       </c>
     </row>
@@ -2614,442 +2614,52 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Puukoolid + seemikumüük</t>
+          <t>Basic income + kriisivarud</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Maaelu, ≠ börs</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E12" s="4">
+          <t>Sotsiaal, defensiivne</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E12" s="3">
         <f>D11*84000000</f>
         <v/>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>30 puukooli</t>
+          <t>10k × 200€ + varud</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Kutsekool + koolitus</t>
+          <t>KOKKU (8 voogu)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Inimkapital</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E13" s="6">
-        <f>D12*84000000</f>
+          <t>Macro 40/30/20/10</t>
+        </is>
+      </c>
+      <c r="D13" s="5">
+        <f>SUM(D4:D11)</f>
+        <v/>
+      </c>
+      <c r="E13" s="5">
+        <f>SUM(E4:E11)</f>
         <v/>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Pipeline töökohtadele</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Operation Mirror säästud</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Bürokraatia efektiivsus</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E14" s="4">
-        <f>D13*84000000</f>
-        <v/>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>~€35M/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>LEADER / EAS / CAP</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Grantid, ≠ börs</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E15" s="6">
-        <f>D14*84000000</f>
-        <v/>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Olemasolev raha</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Urban farm + KOV aiad</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Kohalik kogukond</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E16" s="4">
-        <f>D15*84000000</f>
-        <v/>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Linn + maa</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Teadus + patendid (EPM)</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Pikaajaline</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E17" s="6">
-        <f>D16*84000000</f>
-        <v/>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Eksport tulevikus</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Hampcrete + ehitus</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Ehitustsükkel</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E18" s="4">
-        <f>D17*84000000</f>
-        <v/>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Avalik sektor</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Kriisitoit / varud</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Kriis, defensiivne</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E19" s="6">
-        <f>D18*84000000</f>
-        <v/>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>2-nädala reegel</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Turism + kogemuskeskus</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Hooajaline</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E20" s="4">
-        <f>D19*84000000</f>
-        <v/>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Farm visits</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>IT + IoT kasvatus</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Tehnoloogia</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E21" s="6">
-        <f>D20*84000000</f>
-        <v/>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Efektiivsus</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Basic income pilot</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Sotsiaal</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E22" s="3">
-        <f>D21*84000000</f>
-        <v/>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>10k × 200€/kuu</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>KOKKU (18 voogu)</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Dalio siht: 15–20</t>
-        </is>
-      </c>
-      <c r="D23" s="5">
-        <f>SUM(D4:D21)</f>
-        <v/>
-      </c>
-      <c r="E23" s="5">
-        <f>SUM(E4:E21)</f>
-        <v/>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
           <t>100% Inimeste Fond A5</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
-      <c r="B24" s="3" t="inlineStr"/>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="9" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Macro</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>4 kotti (vanem mudel)</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Endiselt kehtib</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Päikesepargid + salvestus</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E26" s="4">
-        <f>84000000*0.4</f>
-        <v/>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Macro ≠ voogude detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Tööstus + robotid</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr"/>
-      <c r="D27" s="8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E27" s="6">
-        <f>84000000*0.3</f>
-        <v/>
-      </c>
-      <c r="F27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Basic income pilot</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E28">
-        <f>84000000*0.2</f>
-        <v/>
-      </c>
-      <c r="F28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Haridus + koolid + loodus</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E29">
-        <f>84000000*0.1</f>
-        <v/>
-      </c>
-      <c r="F29" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
